--- a/data/indicadores/03_07_02_11_tfa.xlsx
+++ b/data/indicadores/03_07_02_11_tfa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pasantia\atlas ods 2025\Bases de datos indicadores\Finales y con codigo correcto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B2D751D-8FFF-4494-8852-68EDBE6E0004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0CDA89-AC50-44B1-8834-501916E98413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="1" xr2:uid="{81049B06-0AC9-4E3C-871A-12EBFB81BC35}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{81049B06-0AC9-4E3C-871A-12EBFB81BC35}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos originales" sheetId="1" r:id="rId1"/>
@@ -1929,7 +1929,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1978,17 +1978,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2009,11 +2000,15 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2333,104 +2328,104 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="32">
+      <c r="G1" s="28">
         <v>2012</v>
       </c>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32">
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28">
         <v>2024</v>
       </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="31"/>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="32" t="s">
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="32" t="s">
+      <c r="I2" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="32" t="s">
+      <c r="J2" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="32" t="s">
+      <c r="K2" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="32" t="s">
+      <c r="L2" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="32" t="s">
+      <c r="M2" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="32" t="s">
+      <c r="N2" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="32" t="s">
+      <c r="O2" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="32" t="s">
+      <c r="P2" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="Q2" s="32" t="s">
+      <c r="Q2" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="R2" s="32" t="s">
+      <c r="R2" s="28" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="31"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="32"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="28"/>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="28"/>
+      <c r="R3" s="28"/>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1">
@@ -21642,6 +21637,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
     <mergeCell ref="O2:O3"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="Q2:Q3"/>
@@ -21656,12 +21657,6 @@
     <mergeCell ref="L2:L3"/>
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
-    <mergeCell ref="F1:F3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -34514,10 +34509,10 @@
       <c r="B1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="20" t="s">
         <v>548</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="20" t="s">
         <v>549</v>
       </c>
     </row>
@@ -39330,7 +39325,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{482A49AC-40C4-4CAA-A02A-818715AC88C8}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.28515625" customWidth="1"/>
@@ -39339,7 +39334,7 @@
     <col min="4" max="4" width="21.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30">
+    <row r="1" spans="1:6" ht="30">
       <c r="A1" s="17" t="s">
         <v>545</v>
       </c>
@@ -39353,158 +39348,176 @@
         <v>544</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:6">
       <c r="A2" s="18">
         <v>1</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="20">
-        <v>0.2</v>
-      </c>
-      <c r="D2" s="20">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="C2" s="31">
+        <v>0.24987862113610601</v>
+      </c>
+      <c r="D2" s="31">
+        <v>0.13061097256857901</v>
+      </c>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="18">
         <v>2</v>
       </c>
       <c r="B3" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="20">
-        <v>0.2</v>
-      </c>
-      <c r="D3" s="20">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="C3" s="31">
+        <v>0.23411214953271001</v>
+      </c>
+      <c r="D3" s="31">
+        <v>8.9590814766952007E-2</v>
+      </c>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="18">
         <v>3</v>
       </c>
       <c r="B4" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="C4" s="20">
-        <v>0.3</v>
-      </c>
-      <c r="D4" s="20">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="C4" s="31">
+        <v>0.261392687941361</v>
+      </c>
+      <c r="D4" s="31">
+        <v>0.11323692992213601</v>
+      </c>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="18">
         <v>4</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="C5" s="20">
-        <v>0.3</v>
-      </c>
-      <c r="D5" s="20">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="C5" s="31">
+        <v>0.27366654892264197</v>
+      </c>
+      <c r="D5" s="31">
+        <v>8.3214285714285699E-2</v>
+      </c>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="18">
         <v>5</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="C6" s="20">
-        <v>0.3</v>
-      </c>
-      <c r="D6" s="20">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="C6" s="31">
+        <v>0.294060995184591</v>
+      </c>
+      <c r="D6" s="31">
+        <v>0.18734541529882601</v>
+      </c>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="18">
         <v>6</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>313</v>
       </c>
-      <c r="C7" s="20">
-        <v>0.3</v>
-      </c>
-      <c r="D7" s="20">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="C7" s="31">
+        <v>0.25025536261491299</v>
+      </c>
+      <c r="D7" s="31">
+        <v>9.5033891271268503E-2</v>
+      </c>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="18">
         <v>7</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>519</v>
       </c>
-      <c r="C8" s="20">
-        <v>0.3</v>
-      </c>
-      <c r="D8" s="20">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="C8" s="31">
+        <v>0.33459843573356701</v>
+      </c>
+      <c r="D8" s="31">
+        <v>0.159141376757957</v>
+      </c>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="18">
         <v>8</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>397</v>
       </c>
-      <c r="C9" s="20">
-        <v>0.6</v>
-      </c>
-      <c r="D9" s="20">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="C9" s="31">
+        <v>0.55982518347489096</v>
+      </c>
+      <c r="D9" s="31">
+        <v>0.331323904474844</v>
+      </c>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="18">
         <v>9</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>423</v>
       </c>
-      <c r="C10" s="20">
-        <v>0.8</v>
-      </c>
-      <c r="D10" s="20">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="C10" s="31">
+        <v>0.75995807127882598</v>
+      </c>
+      <c r="D10" s="31">
+        <v>0.30352375867592102</v>
+      </c>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="18">
         <v>10</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>317</v>
       </c>
-      <c r="C11" s="23">
-        <v>0.34047675999999999</v>
-      </c>
-      <c r="D11" s="23">
-        <v>0.12904797000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="C11" s="13">
+        <v>0.34047676378521602</v>
+      </c>
+      <c r="D11" s="13">
+        <v>0.129047966885805</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="18">
         <v>11</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>547</v>
       </c>
-      <c r="C12" s="21">
-        <v>0.3</v>
-      </c>
-      <c r="D12" s="20">
-        <v>0.1</v>
+      <c r="C12" s="13">
+        <v>0.29498578968737299</v>
+      </c>
+      <c r="D12" s="13">
+        <v>0.13426657277174001</v>
       </c>
     </row>
   </sheetData>
@@ -39523,16 +39536,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="20" t="s">
         <v>545</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="20" t="s">
         <v>546</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="20" t="s">
         <v>548</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="20" t="s">
         <v>549</v>
       </c>
     </row>
@@ -39543,10 +39556,10 @@
       <c r="B2" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="30">
+      <c r="C2" s="27">
         <v>3752</v>
       </c>
-      <c r="D2" s="30">
+      <c r="D2" s="27">
         <v>2212</v>
       </c>
     </row>
@@ -39557,10 +39570,10 @@
       <c r="B3" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="30">
+      <c r="C3" s="27">
         <v>12807</v>
       </c>
-      <c r="D3" s="30">
+      <c r="D3" s="27">
         <v>6227</v>
       </c>
     </row>
@@ -39571,10 +39584,10 @@
       <c r="B4" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C4" s="27">
         <v>11792</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="27">
         <v>7126</v>
       </c>
     </row>
@@ -39585,10 +39598,10 @@
       <c r="B5" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="27">
         <v>2410</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="27">
         <v>1398</v>
       </c>
     </row>
@@ -39599,10 +39612,10 @@
       <c r="B6" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="27">
         <v>5176</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="27">
         <v>3620</v>
       </c>
     </row>
@@ -39613,10 +39626,10 @@
       <c r="B7" s="19" t="s">
         <v>313</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="27">
         <v>3273</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="27">
         <v>1227</v>
       </c>
     </row>
@@ -39627,10 +39640,10 @@
       <c r="B8" s="19" t="s">
         <v>519</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="27">
         <v>22940</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="27">
         <v>11210</v>
       </c>
     </row>
@@ -39641,10 +39654,10 @@
       <c r="B9" s="19" t="s">
         <v>397</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="27">
         <v>5089</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="27">
         <v>3563</v>
       </c>
     </row>
@@ -39655,10 +39668,10 @@
       <c r="B10" s="19" t="s">
         <v>423</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="27">
         <v>1620</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="27">
         <v>978</v>
       </c>
     </row>
@@ -39669,10 +39682,10 @@
       <c r="B11" s="19" t="s">
         <v>317</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="26">
         <v>1162</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="26">
         <v>467</v>
       </c>
     </row>
@@ -39683,10 +39696,10 @@
       <c r="B12" s="19" t="s">
         <v>547</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="27">
         <v>68859</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="27">
         <v>36500</v>
       </c>
     </row>
@@ -39701,34 +39714,34 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10" ht="48">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="21" t="s">
         <v>550</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="21" t="s">
         <v>551</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="22" t="s">
         <v>552</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="22" t="s">
         <v>553</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="23" t="s">
         <v>554</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="23" t="s">
         <v>555</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="24" t="s">
         <v>556</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="24" t="s">
         <v>557</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="25" t="s">
         <v>558</v>
       </c>
-      <c r="J1" s="28" t="s">
+      <c r="J1" s="25" t="s">
         <v>559</v>
       </c>
     </row>
